--- a/Hoadon/HD2026/HDVao/8/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/8/3502550210_HDDienTuMayTinhTien.xlsx
@@ -1766,32 +1766,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C26MMH</t>
+          <t>C26MMM</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>079078009688</t>
+          <t>079056002409</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH MẠNH HIẾU</t>
+          <t>Cường Hưng</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>606 Tân Kỳ Tân Quý, KP7, P.Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1807,9 +1807,11 @@
       <c r="K28" s="6"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O28" s="13" t="n">
-        <v>2800000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1833,32 +1835,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MMH</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>092196012573</t>
+          <t>079078009688</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NHÂN NHẬT NGUYÊN</t>
+          <t>HỘ KINH DOANH MẠNH HIẾU</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>412/6 đường Trương Công Định, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>606 Tân Kỳ Tân Quý, KP7, P.Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1874,11 +1876,9 @@
       <c r="K29" s="6"/>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
-      <c r="N29" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>4440000.0</v>
+        <v>2800000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1897,37 +1897,37 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>092196012573</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>HỘ KINH DOANH NHÂN NHẬT NGUYÊN</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>412/6 đường Trương Công Định, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -1941,17 +1941,13 @@
         </is>
       </c>
       <c r="K30" s="6"/>
-      <c r="L30" s="13" t="n">
-        <v>3625000.0</v>
-      </c>
-      <c r="M30" s="13" t="n">
-        <v>290000.0</v>
-      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
       <c r="N30" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>3915000.0</v>
+        <v>4440000.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -1980,12 +1976,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>40717</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2015,16 +2011,16 @@
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>4522400.0</v>
+        <v>3625000.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>361792.0</v>
+        <v>290000.0</v>
       </c>
       <c r="N31" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>4884192.0</v>
+        <v>3915000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2053,7 +2049,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>40718</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -2088,16 +2084,16 @@
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>1216704.0</v>
+        <v>4522400.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>97336.0</v>
+        <v>361792.0</v>
       </c>
       <c r="N32" s="13" t="n">
-        <v>17196.0</v>
+        <v>0.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>1314040.0</v>
+        <v>4884192.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2126,12 +2122,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2161,16 +2157,16 @@
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>3953866.0</v>
+        <v>1216704.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>316309.0</v>
+        <v>97336.0</v>
       </c>
       <c r="N33" s="13" t="n">
-        <v>13554.0</v>
+        <v>17196.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>4270175.0</v>
+        <v>1314040.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2199,12 +2195,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>41218</t>
+          <t>41159</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2234,16 +2230,16 @@
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>3740741.0</v>
+        <v>3953866.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>299259.0</v>
+        <v>316309.0</v>
       </c>
       <c r="N34" s="13" t="n">
-        <v>501259.0</v>
+        <v>13554.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>4040000.0</v>
+        <v>4270175.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2272,12 +2268,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>41218</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2307,16 +2303,16 @@
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>6373560.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>509885.0</v>
+        <v>299259.0</v>
       </c>
       <c r="N35" s="13" t="n">
-        <v>122080.0</v>
+        <v>501259.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>6883445.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2345,12 +2341,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>41642</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2380,16 +2376,16 @@
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>3939900.0</v>
+        <v>6373560.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>315192.0</v>
+        <v>509885.0</v>
       </c>
       <c r="N36" s="13" t="n">
-        <v>0.0</v>
+        <v>122080.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>4255092.0</v>
+        <v>6883445.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2418,7 +2414,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -2453,16 +2449,16 @@
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>4048650.0</v>
+        <v>3939900.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>323892.0</v>
+        <v>315192.0</v>
       </c>
       <c r="N37" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>4372542.0</v>
+        <v>4255092.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2491,12 +2487,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>42142</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2526,16 +2522,16 @@
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>1751616.0</v>
+        <v>4048650.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>140129.0</v>
+        <v>323892.0</v>
       </c>
       <c r="N38" s="13" t="n">
-        <v>177984.0</v>
+        <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>1891745.0</v>
+        <v>4372542.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2564,7 +2560,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>42148</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -2599,16 +2595,16 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>3.4722222E7</v>
+        <v>1751616.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>2777778.0</v>
+        <v>140129.0</v>
       </c>
       <c r="N39" s="13" t="n">
-        <v>2057778.0</v>
+        <v>177984.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>3.75E7</v>
+        <v>1891745.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2637,12 +2633,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>42148</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2672,16 +2668,16 @@
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>2.25828E7</v>
+        <v>3.4722222E7</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1806624.0</v>
+        <v>2777778.0</v>
       </c>
       <c r="N40" s="13" t="n">
-        <v>0.0</v>
+        <v>2057778.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>2.4389424E7</v>
+        <v>3.75E7</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2710,7 +2706,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>42547</t>
+          <t>42388</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -2745,16 +2741,16 @@
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>1812294.0</v>
+        <v>2.25828E7</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>144984.0</v>
+        <v>1806624.0</v>
       </c>
       <c r="N41" s="13" t="n">
-        <v>21906.0</v>
+        <v>0.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>1957278.0</v>
+        <v>2.4389424E7</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2783,12 +2779,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>42790</t>
+          <t>42547</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2818,16 +2814,16 @@
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1812294.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>299259.0</v>
+        <v>144984.0</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>501259.0</v>
+        <v>21906.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1957278.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2856,7 +2852,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>42790</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -2891,16 +2887,16 @@
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>6723669.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>537894.0</v>
+        <v>299259.0</v>
       </c>
       <c r="N43" s="13" t="n">
-        <v>41881.0</v>
+        <v>501259.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>7261563.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2929,12 +2925,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2964,16 +2960,16 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>8472222.0</v>
+        <v>6723669.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>677778.0</v>
+        <v>537894.0</v>
       </c>
       <c r="N44" s="13" t="n">
-        <v>383778.0</v>
+        <v>41881.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>9150000.0</v>
+        <v>7261563.0</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -3002,7 +2998,7 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>43433</t>
+          <t>43256</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3037,16 +3033,16 @@
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>6249000.0</v>
+        <v>8472222.0</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>499920.0</v>
+        <v>677778.0</v>
       </c>
       <c r="N45" s="13" t="n">
-        <v>0.0</v>
+        <v>383778.0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>6748920.0</v>
+        <v>9150000.0</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -3075,7 +3071,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>43434</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -3110,16 +3106,16 @@
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="13" t="n">
-        <v>5206970.0</v>
+        <v>6249000.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>416558.0</v>
+        <v>499920.0</v>
       </c>
       <c r="N46" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>5623528.0</v>
+        <v>6748920.0</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -3148,12 +3144,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>43688</t>
+          <t>43434</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3183,16 +3179,16 @@
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>2391991.0</v>
+        <v>5206970.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>191359.0</v>
+        <v>416558.0</v>
       </c>
       <c r="N47" s="13" t="n">
-        <v>69109.0</v>
+        <v>0.0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>2583350.0</v>
+        <v>5623528.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -3216,32 +3212,32 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C26MTP</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>43688</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3251,21 +3247,21 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>1.1363636E7</v>
+        <v>2391991.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>1136364.0</v>
+        <v>191359.0</v>
       </c>
       <c r="N48" s="13" t="n">
-        <v>0.0</v>
+        <v>69109.0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>1.25E7</v>
+        <v>2583350.0</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -3289,32 +3285,32 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C26MTP</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>44081</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -3324,21 +3320,21 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>1.1636363E7</v>
+        <v>4700000.0</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>1163637.0</v>
+        <v>376000.0</v>
       </c>
       <c r="N49" s="13" t="n">
-        <v>0.0</v>
+        <v>607600.0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>1.28E7</v>
+        <v>5076000.0</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -3362,32 +3358,32 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MLQ</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>689</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500728882</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH LONG QUÂN - NHÀ HÀNG QUÁN TRE</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 407-409-411 Thống Nhất, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3402,16 +3398,16 @@
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="13" t="n">
-        <v>1.4967273E7</v>
+        <v>1.5169E7</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>1496727.0</v>
+        <v>1251320.0</v>
       </c>
       <c r="N50" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>1.6464E7</v>
+        <v>1.642032E7</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
@@ -3435,32 +3431,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -3475,16 +3471,16 @@
       </c>
       <c r="K51" s="6"/>
       <c r="L51" s="13" t="n">
-        <v>3.3631818E7</v>
+        <v>7018519.0</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>3363182.0</v>
+        <v>561481.0</v>
       </c>
       <c r="N51" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>3.6995E7</v>
+        <v>7580000.0</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
@@ -3508,32 +3504,32 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -3543,21 +3539,21 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K52" s="6"/>
       <c r="L52" s="13" t="n">
-        <v>4.8272727E7</v>
+        <v>1.1363636E7</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>4827273.0</v>
+        <v>1136364.0</v>
       </c>
       <c r="N52" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>5.31E7</v>
+        <v>1.25E7</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
@@ -3581,32 +3577,32 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -3616,21 +3612,21 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K53" s="6"/>
       <c r="L53" s="13" t="n">
-        <v>6615825.0</v>
+        <v>1.1636363E7</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>609175.0</v>
+        <v>1163637.0</v>
       </c>
       <c r="N53" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O53" s="13" t="n">
-        <v>7225000.0</v>
+        <v>1.28E7</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
@@ -3659,12 +3655,12 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -3694,16 +3690,16 @@
       </c>
       <c r="K54" s="6"/>
       <c r="L54" s="13" t="n">
-        <v>7536364.0</v>
+        <v>1.4967273E7</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>753636.0</v>
+        <v>1496727.0</v>
       </c>
       <c r="N54" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O54" s="13" t="n">
-        <v>8290000.0</v>
+        <v>1.6464E7</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
@@ -3732,12 +3728,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -3767,16 +3763,16 @@
       </c>
       <c r="K55" s="6"/>
       <c r="L55" s="13" t="n">
-        <v>7954545.0</v>
+        <v>3.3631818E7</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>795455.0</v>
+        <v>3363182.0</v>
       </c>
       <c r="N55" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O55" s="13" t="n">
-        <v>8750000.0</v>
+        <v>3.6995E7</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
@@ -3800,32 +3796,32 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -3840,16 +3836,16 @@
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="13" t="n">
-        <v>1402500.0</v>
+        <v>4.8272727E7</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>112200.0</v>
+        <v>4827273.0</v>
       </c>
       <c r="N56" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O56" s="13" t="n">
-        <v>1514700.0</v>
+        <v>5.31E7</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
@@ -3873,32 +3869,32 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -3913,16 +3909,16 @@
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="13" t="n">
-        <v>1037037.0</v>
+        <v>6615825.0</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>82963.0</v>
+        <v>609175.0</v>
       </c>
       <c r="N57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>1120000.0</v>
+        <v>7225000.0</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -3946,32 +3942,32 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -3986,16 +3982,16 @@
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="13" t="n">
-        <v>2078705.0</v>
+        <v>7536364.0</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>166295.0</v>
+        <v>753636.0</v>
       </c>
       <c r="N58" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>2245000.0</v>
+        <v>8290000.0</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
@@ -4019,32 +4015,32 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4059,16 +4055,16 @@
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="13" t="n">
-        <v>1721019.0</v>
+        <v>7954545.0</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>137682.0</v>
+        <v>795455.0</v>
       </c>
       <c r="N59" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>1858701.0</v>
+        <v>8750000.0</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
@@ -4097,12 +4093,12 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -4132,16 +4128,16 @@
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="13" t="n">
-        <v>2353705.0</v>
+        <v>1402500.0</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>188295.0</v>
+        <v>112200.0</v>
       </c>
       <c r="N60" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O60" s="13" t="n">
-        <v>2542000.0</v>
+        <v>1514700.0</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -4165,32 +4161,32 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MDH</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3502425499</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4205,16 +4201,16 @@
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="13" t="n">
-        <v>1848147.0</v>
+        <v>1037037.0</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>147853.0</v>
+        <v>82963.0</v>
       </c>
       <c r="N61" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O61" s="13" t="n">
-        <v>1996000.0</v>
+        <v>1120000.0</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -4238,32 +4234,32 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>C26MTA</t>
+          <t>C26MDH</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3502426622</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4278,16 +4274,16 @@
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="13" t="n">
-        <v>1.9788889E7</v>
+        <v>2078705.0</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>1583111.0</v>
+        <v>166295.0</v>
       </c>
       <c r="N62" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2.1372E7</v>
+        <v>2245000.0</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -4311,32 +4307,32 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MDH</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -4351,16 +4347,16 @@
       </c>
       <c r="K63" s="6"/>
       <c r="L63" s="13" t="n">
-        <v>2727274.0</v>
+        <v>1721019.0</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>272727.0</v>
+        <v>137682.0</v>
       </c>
       <c r="N63" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>3000001.0</v>
+        <v>1858701.0</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -4384,32 +4380,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MDH</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4424,16 +4420,16 @@
       </c>
       <c r="K64" s="6"/>
       <c r="L64" s="13" t="n">
-        <v>2727274.0</v>
+        <v>2353705.0</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>272727.0</v>
+        <v>188295.0</v>
       </c>
       <c r="N64" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O64" s="13" t="n">
-        <v>3000001.0</v>
+        <v>2542000.0</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -4457,32 +4453,32 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502425499</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4497,16 +4493,16 @@
       </c>
       <c r="K65" s="6"/>
       <c r="L65" s="13" t="n">
-        <v>2727274.0</v>
+        <v>1848147.0</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>272727.0</v>
+        <v>147853.0</v>
       </c>
       <c r="N65" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>3000001.0</v>
+        <v>1996000.0</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -4530,32 +4526,32 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTA</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>347</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502426622</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THẢO ANH VŨNG TÀU</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>Tổ 12, ấp Phước Hưng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4565,21 +4561,21 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="13" t="n">
-        <v>1.8E7</v>
+        <v>1.9788889E7</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>1800000.0</v>
+        <v>1583111.0</v>
       </c>
       <c r="N66" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>1.98E7</v>
+        <v>2.1372E7</v>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
@@ -4608,27 +4604,27 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -4638,21 +4634,21 @@
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="13" t="n">
-        <v>2.7090909E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>2709091.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>2.98E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -4681,27 +4677,27 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -4711,25 +4707,25 @@
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="13" t="n">
-        <v>1.8E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>1800000.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N68" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>1.98E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q68" s="6" t="inlineStr">
@@ -4754,27 +4750,27 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -4784,25 +4780,25 @@
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K69" s="6"/>
       <c r="L69" s="13" t="n">
-        <v>1.8E7</v>
+        <v>2727274.0</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>1800000.0</v>
+        <v>272727.0</v>
       </c>
       <c r="N69" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O69" s="13" t="n">
-        <v>1.98E7</v>
+        <v>3000001.0</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
@@ -4822,32 +4818,32 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -4857,21 +4853,21 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="13" t="n">
-        <v>3320000.0</v>
+        <v>1.8E7</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>265600.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="N70" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>3585600.0</v>
+        <v>1.98E7</v>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
@@ -4895,32 +4891,32 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -4930,21 +4926,21 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="13" t="n">
-        <v>5425926.0</v>
+        <v>2.7090909E7</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>434074.0</v>
+        <v>2709091.0</v>
       </c>
       <c r="N71" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>5860000.0</v>
+        <v>2.98E7</v>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
@@ -4968,32 +4964,32 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
@@ -5003,25 +4999,25 @@
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K72" s="6"/>
       <c r="L72" s="13" t="n">
-        <v>1.6574074E7</v>
+        <v>1.8E7</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>1325926.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="N72" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O72" s="13" t="n">
-        <v>1.79E7</v>
+        <v>1.98E7</v>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
@@ -5041,32 +5037,32 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -5076,25 +5072,25 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K73" s="6"/>
       <c r="L73" s="13" t="n">
-        <v>4745926.0</v>
+        <v>1.8E7</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>379674.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="N73" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>5125600.0</v>
+        <v>1.98E7</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
@@ -5119,12 +5115,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -5154,16 +5150,16 @@
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="13" t="n">
-        <v>3166668.0</v>
+        <v>3320000.0</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>253332.0</v>
+        <v>265600.0</v>
       </c>
       <c r="N74" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O74" s="13" t="n">
-        <v>3420000.0</v>
+        <v>3585600.0</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
@@ -5192,12 +5188,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -5227,16 +5223,16 @@
       </c>
       <c r="K75" s="6"/>
       <c r="L75" s="13" t="n">
-        <v>1898148.0</v>
+        <v>5425926.0</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>151852.0</v>
+        <v>434074.0</v>
       </c>
       <c r="N75" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>2050000.0</v>
+        <v>5860000.0</v>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
@@ -5265,12 +5261,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -5300,16 +5296,16 @@
       </c>
       <c r="K76" s="6"/>
       <c r="L76" s="13" t="n">
-        <v>3540000.0</v>
+        <v>1.6574074E7</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>283200.0</v>
+        <v>1325926.0</v>
       </c>
       <c r="N76" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O76" s="13" t="n">
-        <v>3823200.0</v>
+        <v>1.79E7</v>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
@@ -5333,32 +5329,32 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>C26MLH</t>
+          <t>C26MNL</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>3502548042</t>
+          <t>3502547930</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TM DV HỮU TÙNG PHÁT</t>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>KHU PHỐ PHƯỚC HƯNG, PHƯỜNG PHÚ MỸ, THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -5373,23 +5369,388 @@
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="13" t="n">
+        <v>4745926.0</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>379674.0</v>
+      </c>
+      <c r="N77" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>5125600.0</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K78" s="6"/>
+      <c r="L78" s="13" t="n">
+        <v>3166668.0</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>253332.0</v>
+      </c>
+      <c r="N78" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O78" s="13" t="n">
+        <v>3420000.0</v>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K79" s="6"/>
+      <c r="L79" s="13" t="n">
+        <v>1898148.0</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>151852.0</v>
+      </c>
+      <c r="N79" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>2050000.0</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K80" s="6"/>
+      <c r="L80" s="13" t="n">
+        <v>3540000.0</v>
+      </c>
+      <c r="M80" s="13" t="n">
+        <v>283200.0</v>
+      </c>
+      <c r="N80" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O80" s="13" t="n">
+        <v>3823200.0</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K81" s="6"/>
+      <c r="L81" s="13" t="n">
+        <v>333333.0</v>
+      </c>
+      <c r="M81" s="13" t="n">
+        <v>26667.0</v>
+      </c>
+      <c r="N81" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>360000.0</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>3502548042</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TM DV HỮU TÙNG PHÁT</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>KHU PHỐ PHƯỚC HƯNG, PHƯỜNG PHÚ MỸ, THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K82" s="6"/>
+      <c r="L82" s="13" t="n">
         <v>3.5512727E7</v>
       </c>
-      <c r="M77" s="13" t="n">
+      <c r="M82" s="13" t="n">
         <v>3551273.0</v>
       </c>
-      <c r="N77" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O77" s="13" t="n">
+      <c r="N82" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O82" s="13" t="n">
         <v>3.9064E7</v>
       </c>
-      <c r="P77" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q77" s="6" t="inlineStr">
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
